--- a/nac/Modelo_Importacao_Acordos.xlsx
+++ b/nac/Modelo_Importacao_Acordos.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acordos" sheetId="1" r:id="Rded71520a3ff4bf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruções" sheetId="2" r:id="Rf4010a0d1ebb47c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acordos" sheetId="1" r:id="R7a799b505bd64ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruções" sheetId="2" r:id="Ra106ce018256438d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -723,7 +723,7 @@
   </x:sheetData>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="C2:C51">
-      <x:formula1>"Amanda Galdino,Crislayne Vieira,Raissa Correia,Taynã Santos"</x:formula1>
+      <x:formula1>"Amanda Galdino,Crislayne Vieira,Raissa Correia,Taynã Santos,Arruda,Igor Pereira"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -824,7 +824,7 @@
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
       <x:c r="A13" s="4" t="str">
-        <x:v>Negociadoras do NAC</x:v>
+        <x:v>Participantes do painel</x:v>
       </x:c>
       <x:c r="B13" s="4" t="str">
         <x:v>E-mail cadastrado na Central</x:v>
@@ -863,8 +863,28 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="25" customHeight="1">
-      <x:c r="A18" s="1"/>
-      <x:c r="B18" s="1"/>
+      <x:c r="A18" s="1" t="str">
+        <x:v>Arruda</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="str">
+        <x:v>Selecione o nome; não é necessário informar e-mail.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="25" customHeight="1">
+      <x:c r="A19" s="1" t="str">
+        <x:v>Igor Pereira</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="str">
+        <x:v>Selecione o nome; não é necessário informar e-mail.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="25" customHeight="1">
+      <x:c r="A21" s="1" t="str">
+        <x:v>Relatório do sistema</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="str">
+        <x:v>Também pode importar o relatório Realizados NAC completo, pela aba Geral.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
